--- a/Six Sigma Green Belt reports/Historical Data Analysis.xlsx
+++ b/Six Sigma Green Belt reports/Historical Data Analysis.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Parth\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Parth\Documents\GitHub\Financial-Reporting-Process-Transformation\Six Sigma Green Belt reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BBC27C-2173-46F8-9DD1-14CF8B5059D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D49D20-5692-4467-BBB7-ACD92AD03112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="91Days pre implementation data" sheetId="4" r:id="rId1"/>
-    <sheet name="91Days post implementation data" sheetId="5" r:id="rId2"/>
+    <sheet name="91Days pre implementation data" sheetId="7" r:id="rId1"/>
+    <sheet name="50-50 Pre Post Data" sheetId="8" r:id="rId2"/>
+    <sheet name="91Days post implementation data" sheetId="9" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="40">
   <si>
     <t>Date</t>
   </si>
@@ -104,16 +105,75 @@
   <si>
     <t>There are 68 days out of 91 days, where performance is lower than statistical goal. i.e. NC = 74.72%; with DPMO value of 747252.7 and sigma score of -0.66587</t>
   </si>
+  <si>
+    <t>Improve Phase Focus</t>
+  </si>
+  <si>
+    <t>Compliance_Status</t>
+  </si>
+  <si>
+    <t>Implementation_Group</t>
+  </si>
+  <si>
+    <t>≈ 50000</t>
+  </si>
+  <si>
+    <t>SIGMA SCORE 𝜎</t>
+  </si>
+  <si>
+    <t>`+2.00𝜎 to +3.00𝜎</t>
+  </si>
+  <si>
+    <t>WORLD-CLASS BENCHMARK</t>
+  </si>
+  <si>
+    <t>0.0500 (5.0%)</t>
+  </si>
+  <si>
+    <t>&lt; 0.00600 (0.6%)</t>
+  </si>
+  <si>
+    <t>&lt; 6000</t>
+  </si>
+  <si>
+    <t>&gt; +4.5𝜎</t>
+  </si>
+  <si>
+    <t>≈ 50,000</t>
+  </si>
+  <si>
+    <t>&lt; ,6000</t>
+  </si>
+  <si>
+    <t>&lt; 60,00</t>
+  </si>
+  <si>
+    <t>Problem</t>
+  </si>
+  <si>
+    <t>To execute a leftward distribution shift in Daily Reporting Latency, reducing the process median from P50 = 0.4625 hours (27.75 minutes) to the demonstrated benchmark of P25 = 0.029 hours (1.74 minutes) within 3 months. The improvement will standardize demonstrated best performance as the new process midpoint, reduce latency variation, and progress the process toward zero latency defects and ≥6.00σ capability.</t>
+  </si>
+  <si>
+    <t>The Daily Reporting Latency process has a current median of P50 = 0.4625 hours (27.75 minutes), compared with a demonstrated P25 benchmark of 0.029 hours (1.74 minutes). Across the 90-day evaluation period, 47 runs were classified as non-compliant, resulting in a 52.22% non-compliance rate, 522,222.22 DPMO, and a process sigma score of -0.0557σ. This performance remains significantly below the industry average benchmark of approximately 50,000 DPMO (+2.0σ to +3.0σ).</t>
+  </si>
+  <si>
+    <t>INDUSTRY AVERAGE BENCHMARK</t>
+  </si>
+  <si>
+    <t>Preserve the achieved process center at P50 = 0.029 hours and P25 = 0.029 hours while reducing upper-tail variation. Investigate the 8 non-compliant runs for recurring timing, workload, source-system, and handoff causes; standardize the best-performing workflow; automate delay points; and add threshold alerts. Validate improvement over the next 91-day cycle by reducing NCs to no more than 2, DPMO to no more than 22,000, and raising sigma from 1.3537 to at least 2.00 before transition to Control.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,13 +188,46 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="12">
@@ -263,16 +356,41 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -286,7 +404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -301,7 +419,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -322,20 +440,191 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="18">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1D4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -346,6 +635,52 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7F231225-CC95-471F-83B9-9A6D6C047790}" name="Table35" displayName="Table35" ref="A1:D92" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A1:D92" xr:uid="{C654B76E-358A-4873-BC57-8D7A006C23D5}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{4585F7CB-757F-4C3A-B1FC-EE614D6FDADB}" name="Date" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{804AEFA5-508A-4949-AC8B-80BCB4C30237}" name="Daily_Reporting_Latency_Hours" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{B079A7F2-D1D4-4A65-9109-D41191014946}" name="Operational_Phase" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{E73BF206-86CF-4F06-9838-F256C3712153}" name="Compliance_Status" dataDxfId="12">
+      <calculatedColumnFormula>IF(B2&gt;$G$3,"NC","C")</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{45C15661-C4F2-44BE-86A3-53D5EC543CBD}" name="BalancedPrePostData6" displayName="BalancedPrePostData6" ref="A1:E91" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:E91" xr:uid="{6B875B69-748F-4938-ACE6-C2B5CC52ECE7}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{AE33042E-ACF4-4637-A718-2F3390D81F9C}" name="Date" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{2EB70024-7894-4B62-9AB1-FD9FBE7E3007}" name="Daily_Reporting_Latency_Hours" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{43F76E1C-5CE8-4EEB-8858-FA0F5643F47A}" name="Operational_Phase" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{57AA56AB-5E6E-4528-8398-36FC5357D8C2}" name="Compliance_Status" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{F58184A1-5A38-4415-979D-C72230999C89}" name="Implementation_Group" dataDxfId="5">
+      <calculatedColumnFormula>"Post-Implementation"</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A3A4AD3A-5E2E-4BFC-ABFD-328DCF8F375D}" name="Table27" displayName="Table27" ref="A1:D92" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:D92" xr:uid="{2CEB3334-A5C5-44B9-8807-03DE1FD7AEBF}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{0B46FA24-63A4-44D5-92EB-763FB28211DE}" name="Date" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{2466A9E3-DACE-4440-9580-23A9D3DEA069}" name="Daily_Reporting_Latency_Hours" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{F42D0C69-D406-4F43-B57F-7BB1057CF000}" name="Operational_Phase" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{CD833A27-2B16-4C04-B7EF-500ADFD58432}" name="Compliance_Status" dataDxfId="0">
+      <calculatedColumnFormula>IF(B2&gt;$G$3,"NC","C")</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -665,7 +1000,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -686,610 +1021,643 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7F0084-2C14-4314-A88A-1435EDCDDC4F}">
-  <dimension ref="A1:L92"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1D5F02F-37EE-4C96-8F87-70464FACF7E8}">
+  <dimension ref="A1:M92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="12" width="9.140625" style="2"/>
+    <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="4"/>
+    <col min="9" max="9" width="30.7109375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="31" style="4" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D1" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46036</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="7">
         <v>1.25</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="str">
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="str">
         <f>IF(B2&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="4">
         <f>PERCENTILE(B2:B92,0.5)</f>
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46037</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2" t="str">
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4" t="str">
         <f>IF(B3&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="4">
         <f>PERCENTILE(B2:B92,0.25)</f>
         <v>1.0049999999999999</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46038</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="7">
         <v>1.28</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="str">
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="str">
         <f>IF(B4&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46039</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <v>1.41</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="str">
+      <c r="C5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="str">
         <f>IF(B5&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46040</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="7">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="2" t="str">
+      <c r="C6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4" t="str">
         <f>IF(B6&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="F6" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="12"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G6" s="20"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46041</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="7">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2" t="str">
+      <c r="C7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4" t="str">
         <f>IF(B7&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="7">
         <f>COUNTIF(D2:D92,"NC")</f>
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46042</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="7">
         <v>1.42</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2" t="str">
+      <c r="C8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4" t="str">
         <f>IF(B8&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="7">
         <f>COUNT(A2:A92)</f>
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46043</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="7">
         <v>1.3</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2" t="str">
+      <c r="C9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4" t="str">
         <f>IF(B9&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="2">
-        <f>F7/F8</f>
+      <c r="G9" s="8">
+        <f>G7/G8</f>
         <v>0.74725274725274726</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46044</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2" t="str">
+      <c r="C10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="4" t="str">
         <f>IF(B10&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="2">
-        <f>F9*1000000</f>
+      <c r="G10" s="10">
+        <f>G9*1000000</f>
         <v>747252.7472527473</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46045</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="7">
         <v>1.26</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2" t="str">
+      <c r="C11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4" t="str">
         <f>IF(B11&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="2">
-        <f>NORMSINV(1-F9)</f>
+      <c r="F11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="8">
+        <f>NORMSINV(1-G9)</f>
         <v>-0.66586951800104843</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46046</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2" t="str">
+      <c r="C12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="4" t="str">
         <f>IF(B12&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46047</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2" t="str">
+      <c r="C13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4" t="str">
         <f>IF(B13&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46048</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="7">
         <v>1.22</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="2" t="str">
+      <c r="C14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="4" t="str">
         <f>IF(B14&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="F14" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="18"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="26"/>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46049</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="7">
         <v>0.89</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="2" t="str">
+      <c r="C15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="4" t="str">
         <f>IF(B15&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="F15" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="15"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="23"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46050</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="7">
         <v>0.92</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="2" t="str">
+      <c r="C16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="4" t="str">
         <f>IF(B16&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46051</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="2" t="str">
+      <c r="C17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="4" t="str">
         <f>IF(B17&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46052</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="7">
         <v>1.03</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="2" t="str">
+      <c r="C18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="4" t="str">
         <f>IF(B18&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E18" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="18"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46053</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="7">
         <v>1.23</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="2" t="str">
+      <c r="C19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="4" t="str">
         <f>IF(B19&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="5"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46054</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="7">
         <v>1.04</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="2" t="str">
+      <c r="C20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="4" t="str">
         <f>IF(B20&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="8"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46055</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="7">
         <v>0.97</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2" t="str">
+      <c r="C21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4" t="str">
         <f>IF(B21&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="8"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46056</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="7">
         <v>1.4</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2" t="str">
+      <c r="C22" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4" t="str">
         <f>IF(B22&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="8"/>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46057</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="7">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2" t="str">
+      <c r="C23" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4" t="str">
         <f>IF(B23&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="11"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46058</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="7">
         <v>1.19</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2" t="str">
+      <c r="C24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4" t="str">
         <f>IF(B24&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F24" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="26"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46059</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="7">
         <v>0.97</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="2" t="str">
+      <c r="C25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4" t="str">
         <f>IF(B25&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F25" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="13"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46060</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="2" t="str">
+      <c r="C26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="4" t="str">
         <f>IF(B26&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F26" s="14"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="16"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46061</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="7">
         <v>1.2</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="2" t="str">
+      <c r="C27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="4" t="str">
         <f>IF(B27&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F27" s="14"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="16"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46062</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="7">
         <v>1.01</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="2" t="str">
+      <c r="C28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="4" t="str">
         <f>IF(B28&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="16"/>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46063</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="7">
         <v>1.24</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="2" t="str">
+      <c r="C29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="4" t="str">
         <f>IF(B29&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F29" s="17"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="19"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46064</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="7">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="2" t="str">
+      <c r="C30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="4" t="str">
         <f>IF(B30&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46065</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="7">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="2" t="str">
+      <c r="C31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="4" t="str">
         <f>IF(B31&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46066</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="7">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="2" t="str">
+      <c r="C32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="4" t="str">
         <f>IF(B32&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1298,13 +1666,13 @@
       <c r="A33" s="1">
         <v>46067</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="7">
         <v>1.46</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="2" t="str">
+      <c r="C33" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="4" t="str">
         <f>IF(B33&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1313,13 +1681,13 @@
       <c r="A34" s="1">
         <v>46068</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="7">
         <v>1.18</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="2" t="str">
+      <c r="C34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="4" t="str">
         <f>IF(B34&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1328,13 +1696,13 @@
       <c r="A35" s="1">
         <v>46069</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="7">
         <v>1.02</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="2" t="str">
+      <c r="C35" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="4" t="str">
         <f>IF(B35&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1343,13 +1711,13 @@
       <c r="A36" s="1">
         <v>46070</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="7">
         <v>1.3</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="2" t="str">
+      <c r="C36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="4" t="str">
         <f>IF(B36&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1358,13 +1726,13 @@
       <c r="A37" s="1">
         <v>46071</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="7">
         <v>1</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="2" t="str">
+      <c r="C37" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="4" t="str">
         <f>IF(B37&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -1373,13 +1741,13 @@
       <c r="A38" s="1">
         <v>46072</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="7">
         <v>1.21</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="2" t="str">
+      <c r="C38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="4" t="str">
         <f>IF(B38&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1388,13 +1756,13 @@
       <c r="A39" s="1">
         <v>46073</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="7">
         <v>0.89</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="2" t="str">
+      <c r="C39" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="4" t="str">
         <f>IF(B39&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -1403,13 +1771,13 @@
       <c r="A40" s="1">
         <v>46074</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="7">
         <v>0.98</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="2" t="str">
+      <c r="C40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="4" t="str">
         <f>IF(B40&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -1418,13 +1786,13 @@
       <c r="A41" s="1">
         <v>46075</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="7">
         <v>1.21</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="2" t="str">
+      <c r="C41" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="4" t="str">
         <f>IF(B41&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1433,13 +1801,13 @@
       <c r="A42" s="1">
         <v>46076</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="7">
         <v>1.29</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="2" t="str">
+      <c r="C42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="4" t="str">
         <f>IF(B42&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1448,13 +1816,13 @@
       <c r="A43" s="1">
         <v>46077</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="7">
         <v>1.21</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="2" t="str">
+      <c r="C43" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="4" t="str">
         <f>IF(B43&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1463,13 +1831,13 @@
       <c r="A44" s="1">
         <v>46078</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="7">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="2" t="str">
+      <c r="C44" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="4" t="str">
         <f>IF(B44&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1478,13 +1846,13 @@
       <c r="A45" s="1">
         <v>46079</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="7">
         <v>1.1299999999999999</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="2" t="str">
+      <c r="C45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="4" t="str">
         <f>IF(B45&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1493,13 +1861,13 @@
       <c r="A46" s="1">
         <v>46080</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="7">
         <v>0.96</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="2" t="str">
+      <c r="C46" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="4" t="str">
         <f>IF(B46&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -1508,13 +1876,13 @@
       <c r="A47" s="1">
         <v>46081</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="7">
         <v>1.07</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="2" t="str">
+      <c r="C47" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="4" t="str">
         <f>IF(B47&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1523,13 +1891,13 @@
       <c r="A48" s="1">
         <v>46082</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="2" t="str">
+      <c r="C48" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="4" t="str">
         <f>IF(B48&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1538,13 +1906,13 @@
       <c r="A49" s="1">
         <v>46083</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="7">
         <v>1.34</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="2" t="str">
+      <c r="C49" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="4" t="str">
         <f>IF(B49&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1553,13 +1921,13 @@
       <c r="A50" s="1">
         <v>46084</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="7">
         <v>1.23</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="2" t="str">
+      <c r="C50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="4" t="str">
         <f>IF(B50&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1568,13 +1936,13 @@
       <c r="A51" s="1">
         <v>46085</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="7">
         <v>0.92</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="2" t="str">
+      <c r="C51" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="4" t="str">
         <f>IF(B51&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -1583,13 +1951,13 @@
       <c r="A52" s="1">
         <v>46086</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="7">
         <v>1.23</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="2" t="str">
+      <c r="C52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="4" t="str">
         <f>IF(B52&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1598,13 +1966,13 @@
       <c r="A53" s="1">
         <v>46087</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="7">
         <v>1.1200000000000001</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="2" t="str">
+      <c r="C53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="4" t="str">
         <f>IF(B53&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1613,13 +1981,13 @@
       <c r="A54" s="1">
         <v>46088</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="7">
         <v>1.08</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="2" t="str">
+      <c r="C54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="4" t="str">
         <f>IF(B54&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1628,13 +1996,13 @@
       <c r="A55" s="1">
         <v>46089</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="7">
         <v>1.27</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="2" t="str">
+      <c r="C55" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="4" t="str">
         <f>IF(B55&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1643,13 +2011,13 @@
       <c r="A56" s="1">
         <v>46090</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="7">
         <v>1.33</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="2" t="str">
+      <c r="C56" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="4" t="str">
         <f>IF(B56&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1658,13 +2026,13 @@
       <c r="A57" s="1">
         <v>46091</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="7">
         <v>1.32</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="2" t="str">
+      <c r="C57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="4" t="str">
         <f>IF(B57&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1673,13 +2041,13 @@
       <c r="A58" s="1">
         <v>46092</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="7">
         <v>1.05</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="2" t="str">
+      <c r="C58" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="4" t="str">
         <f>IF(B58&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1688,13 +2056,13 @@
       <c r="A59" s="1">
         <v>46093</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="7">
         <v>1.1299999999999999</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="2" t="str">
+      <c r="C59" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="4" t="str">
         <f>IF(B59&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1703,13 +2071,13 @@
       <c r="A60" s="1">
         <v>46094</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="7">
         <v>1.23</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="2" t="str">
+      <c r="C60" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="4" t="str">
         <f>IF(B60&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1718,13 +2086,13 @@
       <c r="A61" s="1">
         <v>46095</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="7">
         <v>1.33</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="2" t="str">
+      <c r="C61" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="4" t="str">
         <f>IF(B61&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1733,13 +2101,13 @@
       <c r="A62" s="1">
         <v>46096</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="2" t="str">
+      <c r="C62" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="4" t="str">
         <f>IF(B62&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1748,13 +2116,13 @@
       <c r="A63" s="1">
         <v>46097</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="7">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="2" t="str">
+      <c r="C63" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="4" t="str">
         <f>IF(B63&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1763,13 +2131,13 @@
       <c r="A64" s="1">
         <v>46098</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="7">
         <v>1.01</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="2" t="str">
+      <c r="C64" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="4" t="str">
         <f>IF(B64&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1778,13 +2146,13 @@
       <c r="A65" s="1">
         <v>46099</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="7">
         <v>1</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="2" t="str">
+      <c r="C65" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="4" t="str">
         <f>IF(B65&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -1793,13 +2161,13 @@
       <c r="A66" s="1">
         <v>46100</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="7">
         <v>1.3</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="2" t="str">
+      <c r="C66" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="4" t="str">
         <f>IF(B66&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1808,13 +2176,13 @@
       <c r="A67" s="1">
         <v>46101</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="7">
         <v>1.38</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="2" t="str">
+      <c r="C67" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="4" t="str">
         <f>IF(B67&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1823,13 +2191,13 @@
       <c r="A68" s="1">
         <v>46102</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="7">
         <v>1.17</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="2" t="str">
+      <c r="C68" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="4" t="str">
         <f>IF(B68&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1838,13 +2206,13 @@
       <c r="A69" s="1">
         <v>46103</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="7">
         <v>1.33</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="2" t="str">
+      <c r="C69" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="4" t="str">
         <f>IF(B69&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1853,13 +2221,13 @@
       <c r="A70" s="1">
         <v>46104</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="7">
         <v>2.37</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D70" s="2" t="str">
+      <c r="D70" s="4" t="str">
         <f>IF(B70&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1868,13 +2236,13 @@
       <c r="A71" s="1">
         <v>46105</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="7">
         <v>2.46</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D71" s="2" t="str">
+      <c r="D71" s="4" t="str">
         <f>IF(B71&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1883,13 +2251,13 @@
       <c r="A72" s="1">
         <v>46106</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="7">
         <v>2.21</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D72" s="2" t="str">
+      <c r="D72" s="4" t="str">
         <f>IF(B72&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1898,13 +2266,13 @@
       <c r="A73" s="1">
         <v>46107</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="7">
         <v>2.46</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D73" s="2" t="str">
+      <c r="D73" s="4" t="str">
         <f>IF(B73&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1913,13 +2281,13 @@
       <c r="A74" s="1">
         <v>46108</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="7">
         <v>2.21</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D74" s="2" t="str">
+      <c r="D74" s="4" t="str">
         <f>IF(B74&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1928,13 +2296,13 @@
       <c r="A75" s="1">
         <v>46109</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="7">
         <v>2.4700000000000002</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D75" s="2" t="str">
+      <c r="D75" s="4" t="str">
         <f>IF(B75&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1943,13 +2311,13 @@
       <c r="A76" s="1">
         <v>46110</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="7">
         <v>2.7</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D76" s="2" t="str">
+      <c r="D76" s="4" t="str">
         <f>IF(B76&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1958,13 +2326,13 @@
       <c r="A77" s="1">
         <v>46111</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="7">
         <v>2.37</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D77" s="2" t="str">
+      <c r="D77" s="4" t="str">
         <f>IF(B77&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1973,13 +2341,13 @@
       <c r="A78" s="1">
         <v>46112</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="7">
         <v>1.72</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D78" s="2" t="str">
+      <c r="D78" s="4" t="str">
         <f>IF(B78&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -1988,13 +2356,13 @@
       <c r="A79" s="1">
         <v>46113</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D79" s="2" t="str">
+      <c r="D79" s="4" t="str">
         <f>IF(B79&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
@@ -2003,13 +2371,13 @@
       <c r="A80" s="1">
         <v>46114</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="7">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D80" s="2" t="str">
+      <c r="D80" s="4" t="str">
         <f>IF(B80&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2018,13 +2386,13 @@
       <c r="A81" s="1">
         <v>46115</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="7">
         <v>2.3E-2</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D81" s="2" t="str">
+      <c r="C81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" s="4" t="str">
         <f>IF(B81&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2033,13 +2401,13 @@
       <c r="A82" s="1">
         <v>46116</v>
       </c>
-      <c r="B82" s="2">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D82" s="2" t="str">
+      <c r="B82" s="7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" s="4" t="str">
         <f>IF(B82&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2048,13 +2416,13 @@
       <c r="A83" s="1">
         <v>46117</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="7">
         <v>3.1E-2</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D83" s="2" t="str">
+      <c r="C83" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="4" t="str">
         <f>IF(B83&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2063,13 +2431,13 @@
       <c r="A84" s="1">
         <v>46118</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="7">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D84" s="2" t="str">
+      <c r="C84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="4" t="str">
         <f>IF(B84&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2078,13 +2446,13 @@
       <c r="A85" s="1">
         <v>46119</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="7">
         <v>2.7E-2</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D85" s="2" t="str">
+      <c r="C85" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="4" t="str">
         <f>IF(B85&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2093,13 +2461,13 @@
       <c r="A86" s="1">
         <v>46120</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="7">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D86" s="2" t="str">
+      <c r="C86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" s="4" t="str">
         <f>IF(B86&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2108,13 +2476,13 @@
       <c r="A87" s="1">
         <v>46121</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="7">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D87" s="2" t="str">
+      <c r="C87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="4" t="str">
         <f>IF(B87&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2123,13 +2491,13 @@
       <c r="A88" s="1">
         <v>46122</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88" s="7">
         <v>3.1E-2</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D88" s="2" t="str">
+      <c r="C88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D88" s="4" t="str">
         <f>IF(B88&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2138,13 +2506,13 @@
       <c r="A89" s="1">
         <v>46123</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" s="7">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D89" s="2" t="str">
+      <c r="C89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" s="4" t="str">
         <f>IF(B89&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2153,13 +2521,13 @@
       <c r="A90" s="1">
         <v>46124</v>
       </c>
-      <c r="B90" s="2">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D90" s="2" t="str">
+      <c r="B90" s="7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="4" t="str">
         <f>IF(B90&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2168,13 +2536,13 @@
       <c r="A91" s="1">
         <v>46125</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="7">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D91" s="2" t="str">
+      <c r="C91" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" s="4" t="str">
         <f>IF(B91&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2183,658 +2551,3042 @@
       <c r="A92" s="1">
         <v>46126</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92" s="7">
         <v>0.03</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D92" s="2" t="str">
+      <c r="C92" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" s="4" t="str">
         <f>IF(B92&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="E19:K23"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E15:K15"/>
-    <mergeCell ref="E14:K14"/>
-    <mergeCell ref="E18:K18"/>
+    <mergeCell ref="F25:L29"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F15:L15"/>
+    <mergeCell ref="F14:L14"/>
+    <mergeCell ref="F24:L24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A1198E-E854-4428-94E6-2C6933EF6991}">
-  <dimension ref="A1:L92"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8755C0C-4E24-4560-B5C3-605B67BE770F}">
+  <sheetPr>
+    <tabColor rgb="FF4472C4"/>
+  </sheetPr>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="12" width="9.140625" style="2"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="9" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="31" customWidth="1"/>
+    <col min="11" max="11" width="29.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="30">
+        <f>'91Days pre implementation data'!A35</f>
+        <v>46069</v>
+      </c>
+      <c r="B2" s="29">
+        <f>'91Days pre implementation data'!B35</f>
+        <v>1.02</v>
+      </c>
+      <c r="C2" t="str">
+        <f>'91Days pre implementation data'!C35</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D2" t="str">
+        <f>'91Days pre implementation data'!D35</f>
+        <v>NC</v>
+      </c>
+      <c r="E2" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F2" s="28"/>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="4">
+        <f>PERCENTILE(B2:B92,0.5)</f>
+        <v>0.46250000000000002</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="30">
+        <f>'91Days pre implementation data'!A36</f>
+        <v>46070</v>
+      </c>
+      <c r="B3" s="29">
+        <f>'91Days pre implementation data'!B36</f>
+        <v>1.3</v>
+      </c>
+      <c r="C3" t="str">
+        <f>'91Days pre implementation data'!C36</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D3" t="str">
+        <f>'91Days pre implementation data'!D36</f>
+        <v>NC</v>
+      </c>
+      <c r="E3" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F3" s="28"/>
+      <c r="G3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="4">
+        <f>PERCENTILE(B2:B92,0.25)</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="30">
+        <f>'91Days pre implementation data'!A37</f>
+        <v>46071</v>
+      </c>
+      <c r="B4" s="29">
+        <f>'91Days pre implementation data'!B37</f>
+        <v>1</v>
+      </c>
+      <c r="C4" t="str">
+        <f>'91Days pre implementation data'!C37</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D4" t="str">
+        <f>'91Days pre implementation data'!D37</f>
+        <v>C</v>
+      </c>
+      <c r="E4" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F4" s="28"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="30">
+        <f>'91Days pre implementation data'!A38</f>
+        <v>46072</v>
+      </c>
+      <c r="B5" s="29">
+        <f>'91Days pre implementation data'!B38</f>
+        <v>1.21</v>
+      </c>
+      <c r="C5" t="str">
+        <f>'91Days pre implementation data'!C38</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D5" t="str">
+        <f>'91Days pre implementation data'!D38</f>
+        <v>NC</v>
+      </c>
+      <c r="E5" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F5" s="28"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="30">
+        <f>'91Days pre implementation data'!A39</f>
+        <v>46073</v>
+      </c>
+      <c r="B6" s="29">
+        <f>'91Days pre implementation data'!B39</f>
+        <v>0.89</v>
+      </c>
+      <c r="C6" t="str">
+        <f>'91Days pre implementation data'!C39</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D6" t="str">
+        <f>'91Days pre implementation data'!D39</f>
+        <v>C</v>
+      </c>
+      <c r="E6" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F6" s="28"/>
+      <c r="G6" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="4"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="30">
+        <f>'91Days pre implementation data'!A40</f>
+        <v>46074</v>
+      </c>
+      <c r="B7" s="29">
+        <f>'91Days pre implementation data'!B40</f>
+        <v>0.98</v>
+      </c>
+      <c r="C7" t="str">
+        <f>'91Days pre implementation data'!C40</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D7" t="str">
+        <f>'91Days pre implementation data'!D40</f>
+        <v>C</v>
+      </c>
+      <c r="E7" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F7" s="28"/>
+      <c r="G7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="4">
+        <f>COUNTIF(D2:D92,"NC")</f>
+        <v>47</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="30">
+        <f>'91Days pre implementation data'!A41</f>
+        <v>46075</v>
+      </c>
+      <c r="B8" s="29">
+        <f>'91Days pre implementation data'!B41</f>
+        <v>1.21</v>
+      </c>
+      <c r="C8" t="str">
+        <f>'91Days pre implementation data'!C41</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D8" t="str">
+        <f>'91Days pre implementation data'!D41</f>
+        <v>NC</v>
+      </c>
+      <c r="E8" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F8" s="28"/>
+      <c r="G8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNT(A2:A92)</f>
+        <v>90</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="30">
+        <f>'91Days pre implementation data'!A42</f>
+        <v>46076</v>
+      </c>
+      <c r="B9" s="29">
+        <f>'91Days pre implementation data'!B42</f>
+        <v>1.29</v>
+      </c>
+      <c r="C9" t="str">
+        <f>'91Days pre implementation data'!C42</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D9" t="str">
+        <f>'91Days pre implementation data'!D42</f>
+        <v>NC</v>
+      </c>
+      <c r="E9" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F9" s="28"/>
+      <c r="G9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="8">
+        <f>H7/H8</f>
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="4"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="30">
+        <f>'91Days pre implementation data'!A43</f>
+        <v>46077</v>
+      </c>
+      <c r="B10" s="29">
+        <f>'91Days pre implementation data'!B43</f>
+        <v>1.21</v>
+      </c>
+      <c r="C10" t="str">
+        <f>'91Days pre implementation data'!C43</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D10" t="str">
+        <f>'91Days pre implementation data'!D43</f>
+        <v>NC</v>
+      </c>
+      <c r="E10" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F10" s="28"/>
+      <c r="G10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="10">
+        <f>H9*1000000</f>
+        <v>522222.22222222225</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="30">
+        <f>'91Days pre implementation data'!A44</f>
+        <v>46078</v>
+      </c>
+      <c r="B11" s="29">
+        <f>'91Days pre implementation data'!B44</f>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="C11" t="str">
+        <f>'91Days pre implementation data'!C44</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D11" t="str">
+        <f>'91Days pre implementation data'!D44</f>
+        <v>NC</v>
+      </c>
+      <c r="E11" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F11" s="28"/>
+      <c r="G11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="8">
+        <f>NORMSINV(1-H9)</f>
+        <v>-5.5731687742979895E-2</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="30">
+        <f>'91Days pre implementation data'!A45</f>
+        <v>46079</v>
+      </c>
+      <c r="B12" s="29">
+        <f>'91Days pre implementation data'!B45</f>
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C12" t="str">
+        <f>'91Days pre implementation data'!C45</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D12" t="str">
+        <f>'91Days pre implementation data'!D45</f>
+        <v>NC</v>
+      </c>
+      <c r="E12" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F12" s="28"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="30">
+        <f>'91Days pre implementation data'!A46</f>
+        <v>46080</v>
+      </c>
+      <c r="B13" s="29">
+        <f>'91Days pre implementation data'!B46</f>
+        <v>0.96</v>
+      </c>
+      <c r="C13" t="str">
+        <f>'91Days pre implementation data'!C46</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D13" t="str">
+        <f>'91Days pre implementation data'!D46</f>
+        <v>C</v>
+      </c>
+      <c r="E13" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F13" s="28"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+    </row>
+    <row r="14" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="30">
+        <f>'91Days pre implementation data'!A47</f>
+        <v>46081</v>
+      </c>
+      <c r="B14" s="29">
+        <f>'91Days pre implementation data'!B47</f>
+        <v>1.07</v>
+      </c>
+      <c r="C14" t="str">
+        <f>'91Days pre implementation data'!C47</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D14" t="str">
+        <f>'91Days pre implementation data'!D47</f>
+        <v>NC</v>
+      </c>
+      <c r="E14" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F14" s="28"/>
+      <c r="G14" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="26"/>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="30">
+        <f>'91Days pre implementation data'!A48</f>
+        <v>46082</v>
+      </c>
+      <c r="B15" s="29">
+        <f>'91Days pre implementation data'!B48</f>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C15" t="str">
+        <f>'91Days pre implementation data'!C48</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D15" t="str">
+        <f>'91Days pre implementation data'!D48</f>
+        <v>NC</v>
+      </c>
+      <c r="E15" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F15" s="28"/>
+      <c r="G15" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="13"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="30">
+        <f>'91Days pre implementation data'!A49</f>
+        <v>46083</v>
+      </c>
+      <c r="B16" s="29">
+        <f>'91Days pre implementation data'!B49</f>
+        <v>1.34</v>
+      </c>
+      <c r="C16" t="str">
+        <f>'91Days pre implementation data'!C49</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D16" t="str">
+        <f>'91Days pre implementation data'!D49</f>
+        <v>NC</v>
+      </c>
+      <c r="E16" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F16" s="28"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="16"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="30">
+        <f>'91Days pre implementation data'!A50</f>
+        <v>46084</v>
+      </c>
+      <c r="B17" s="29">
+        <f>'91Days pre implementation data'!B50</f>
+        <v>1.23</v>
+      </c>
+      <c r="C17" t="str">
+        <f>'91Days pre implementation data'!C50</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D17" t="str">
+        <f>'91Days pre implementation data'!D50</f>
+        <v>NC</v>
+      </c>
+      <c r="E17" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F17" s="28"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="16"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="30">
+        <f>'91Days pre implementation data'!A51</f>
+        <v>46085</v>
+      </c>
+      <c r="B18" s="29">
+        <f>'91Days pre implementation data'!B51</f>
+        <v>0.92</v>
+      </c>
+      <c r="C18" t="str">
+        <f>'91Days pre implementation data'!C51</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D18" t="str">
+        <f>'91Days pre implementation data'!D51</f>
+        <v>C</v>
+      </c>
+      <c r="E18" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F18" s="28"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="16"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="30">
+        <f>'91Days pre implementation data'!A52</f>
+        <v>46086</v>
+      </c>
+      <c r="B19" s="29">
+        <f>'91Days pre implementation data'!B52</f>
+        <v>1.23</v>
+      </c>
+      <c r="C19" t="str">
+        <f>'91Days pre implementation data'!C52</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D19" t="str">
+        <f>'91Days pre implementation data'!D52</f>
+        <v>NC</v>
+      </c>
+      <c r="E19" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F19" s="28"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="19"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="30">
+        <f>'91Days pre implementation data'!A53</f>
+        <v>46087</v>
+      </c>
+      <c r="B20" s="29">
+        <f>'91Days pre implementation data'!B53</f>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C20" t="str">
+        <f>'91Days pre implementation data'!C53</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D20" t="str">
+        <f>'91Days pre implementation data'!D53</f>
+        <v>NC</v>
+      </c>
+      <c r="E20" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F20" s="28"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="30">
+        <f>'91Days pre implementation data'!A54</f>
+        <v>46088</v>
+      </c>
+      <c r="B21" s="29">
+        <f>'91Days pre implementation data'!B54</f>
+        <v>1.08</v>
+      </c>
+      <c r="C21" t="str">
+        <f>'91Days pre implementation data'!C54</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D21" t="str">
+        <f>'91Days pre implementation data'!D54</f>
+        <v>NC</v>
+      </c>
+      <c r="E21" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F21" s="28"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="30">
+        <f>'91Days pre implementation data'!A55</f>
+        <v>46089</v>
+      </c>
+      <c r="B22" s="29">
+        <f>'91Days pre implementation data'!B55</f>
+        <v>1.27</v>
+      </c>
+      <c r="C22" t="str">
+        <f>'91Days pre implementation data'!C55</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D22" t="str">
+        <f>'91Days pre implementation data'!D55</f>
+        <v>NC</v>
+      </c>
+      <c r="E22" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F22" s="28"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="30">
+        <f>'91Days pre implementation data'!A56</f>
+        <v>46090</v>
+      </c>
+      <c r="B23" s="29">
+        <f>'91Days pre implementation data'!B56</f>
+        <v>1.33</v>
+      </c>
+      <c r="C23" t="str">
+        <f>'91Days pre implementation data'!C56</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D23" t="str">
+        <f>'91Days pre implementation data'!D56</f>
+        <v>NC</v>
+      </c>
+      <c r="E23" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F23" s="28"/>
+    </row>
+    <row r="24" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="30">
+        <f>'91Days pre implementation data'!A57</f>
+        <v>46091</v>
+      </c>
+      <c r="B24" s="29">
+        <f>'91Days pre implementation data'!B57</f>
+        <v>1.32</v>
+      </c>
+      <c r="C24" t="str">
+        <f>'91Days pre implementation data'!C57</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D24" t="str">
+        <f>'91Days pre implementation data'!D57</f>
+        <v>NC</v>
+      </c>
+      <c r="E24" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F24" s="28"/>
+      <c r="G24" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="26"/>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="30">
+        <f>'91Days pre implementation data'!A58</f>
+        <v>46092</v>
+      </c>
+      <c r="B25" s="29">
+        <f>'91Days pre implementation data'!B58</f>
+        <v>1.05</v>
+      </c>
+      <c r="C25" t="str">
+        <f>'91Days pre implementation data'!C58</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D25" t="str">
+        <f>'91Days pre implementation data'!D58</f>
+        <v>NC</v>
+      </c>
+      <c r="E25" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F25" s="28"/>
+      <c r="G25" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="13"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="30">
+        <f>'91Days pre implementation data'!A59</f>
+        <v>46093</v>
+      </c>
+      <c r="B26" s="29">
+        <f>'91Days pre implementation data'!B59</f>
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C26" t="str">
+        <f>'91Days pre implementation data'!C59</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D26" t="str">
+        <f>'91Days pre implementation data'!D59</f>
+        <v>NC</v>
+      </c>
+      <c r="E26" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F26" s="28"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="16"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="30">
+        <f>'91Days pre implementation data'!A60</f>
+        <v>46094</v>
+      </c>
+      <c r="B27" s="29">
+        <f>'91Days pre implementation data'!B60</f>
+        <v>1.23</v>
+      </c>
+      <c r="C27" t="str">
+        <f>'91Days pre implementation data'!C60</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D27" t="str">
+        <f>'91Days pre implementation data'!D60</f>
+        <v>NC</v>
+      </c>
+      <c r="E27" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F27" s="28"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="16"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="30">
+        <f>'91Days pre implementation data'!A61</f>
+        <v>46095</v>
+      </c>
+      <c r="B28" s="29">
+        <f>'91Days pre implementation data'!B61</f>
+        <v>1.33</v>
+      </c>
+      <c r="C28" t="str">
+        <f>'91Days pre implementation data'!C61</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D28" t="str">
+        <f>'91Days pre implementation data'!D61</f>
+        <v>NC</v>
+      </c>
+      <c r="E28" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F28" s="28"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="16"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="30">
+        <f>'91Days pre implementation data'!A62</f>
+        <v>46096</v>
+      </c>
+      <c r="B29" s="29">
+        <f>'91Days pre implementation data'!B62</f>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C29" t="str">
+        <f>'91Days pre implementation data'!C62</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D29" t="str">
+        <f>'91Days pre implementation data'!D62</f>
+        <v>NC</v>
+      </c>
+      <c r="E29" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F29" s="28"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="16"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="30">
+        <f>'91Days pre implementation data'!A63</f>
+        <v>46097</v>
+      </c>
+      <c r="B30" s="29">
+        <f>'91Days pre implementation data'!B63</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="C30" t="str">
+        <f>'91Days pre implementation data'!C63</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D30" t="str">
+        <f>'91Days pre implementation data'!D63</f>
+        <v>NC</v>
+      </c>
+      <c r="E30" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F30" s="28"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="16"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="30">
+        <f>'91Days pre implementation data'!A64</f>
+        <v>46098</v>
+      </c>
+      <c r="B31" s="29">
+        <f>'91Days pre implementation data'!B64</f>
+        <v>1.01</v>
+      </c>
+      <c r="C31" t="str">
+        <f>'91Days pre implementation data'!C64</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D31" t="str">
+        <f>'91Days pre implementation data'!D64</f>
+        <v>NC</v>
+      </c>
+      <c r="E31" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F31" s="28"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="16"/>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="30">
+        <f>'91Days pre implementation data'!A65</f>
+        <v>46099</v>
+      </c>
+      <c r="B32" s="29">
+        <f>'91Days pre implementation data'!B65</f>
+        <v>1</v>
+      </c>
+      <c r="C32" t="str">
+        <f>'91Days pre implementation data'!C65</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D32" t="str">
+        <f>'91Days pre implementation data'!D65</f>
+        <v>C</v>
+      </c>
+      <c r="E32" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F32" s="28"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="19"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="30">
+        <f>'91Days pre implementation data'!A66</f>
+        <v>46100</v>
+      </c>
+      <c r="B33" s="29">
+        <f>'91Days pre implementation data'!B66</f>
+        <v>1.3</v>
+      </c>
+      <c r="C33" t="str">
+        <f>'91Days pre implementation data'!C66</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D33" t="str">
+        <f>'91Days pre implementation data'!D66</f>
+        <v>NC</v>
+      </c>
+      <c r="E33" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="30">
+        <f>'91Days pre implementation data'!A67</f>
+        <v>46101</v>
+      </c>
+      <c r="B34" s="29">
+        <f>'91Days pre implementation data'!B67</f>
+        <v>1.38</v>
+      </c>
+      <c r="C34" t="str">
+        <f>'91Days pre implementation data'!C67</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D34" t="str">
+        <f>'91Days pre implementation data'!D67</f>
+        <v>NC</v>
+      </c>
+      <c r="E34" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F34" s="28"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="30">
+        <f>'91Days pre implementation data'!A68</f>
+        <v>46102</v>
+      </c>
+      <c r="B35" s="29">
+        <f>'91Days pre implementation data'!B68</f>
+        <v>1.17</v>
+      </c>
+      <c r="C35" t="str">
+        <f>'91Days pre implementation data'!C68</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D35" t="str">
+        <f>'91Days pre implementation data'!D68</f>
+        <v>NC</v>
+      </c>
+      <c r="E35" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F35" s="28"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="30">
+        <f>'91Days pre implementation data'!A69</f>
+        <v>46103</v>
+      </c>
+      <c r="B36" s="29">
+        <f>'91Days pre implementation data'!B69</f>
+        <v>1.33</v>
+      </c>
+      <c r="C36" t="str">
+        <f>'91Days pre implementation data'!C69</f>
+        <v>Historical Baseline Run-Rate</v>
+      </c>
+      <c r="D36" t="str">
+        <f>'91Days pre implementation data'!D69</f>
+        <v>NC</v>
+      </c>
+      <c r="E36" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F36" s="28"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="30">
+        <f>'91Days pre implementation data'!A70</f>
+        <v>46104</v>
+      </c>
+      <c r="B37" s="29">
+        <f>'91Days pre implementation data'!B70</f>
+        <v>2.37</v>
+      </c>
+      <c r="C37" t="str">
+        <f>'91Days pre implementation data'!C70</f>
+        <v>Pre-Implementation Crisis Spike</v>
+      </c>
+      <c r="D37" t="str">
+        <f>'91Days pre implementation data'!D70</f>
+        <v>NC</v>
+      </c>
+      <c r="E37" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F37" s="28"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="30">
+        <f>'91Days pre implementation data'!A71</f>
+        <v>46105</v>
+      </c>
+      <c r="B38" s="29">
+        <f>'91Days pre implementation data'!B71</f>
+        <v>2.46</v>
+      </c>
+      <c r="C38" t="str">
+        <f>'91Days pre implementation data'!C71</f>
+        <v>Pre-Implementation Crisis Spike</v>
+      </c>
+      <c r="D38" t="str">
+        <f>'91Days pre implementation data'!D71</f>
+        <v>NC</v>
+      </c>
+      <c r="E38" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="30">
+        <f>'91Days pre implementation data'!A72</f>
+        <v>46106</v>
+      </c>
+      <c r="B39" s="29">
+        <f>'91Days pre implementation data'!B72</f>
+        <v>2.21</v>
+      </c>
+      <c r="C39" t="str">
+        <f>'91Days pre implementation data'!C72</f>
+        <v>Pre-Implementation Crisis Spike</v>
+      </c>
+      <c r="D39" t="str">
+        <f>'91Days pre implementation data'!D72</f>
+        <v>NC</v>
+      </c>
+      <c r="E39" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F39" s="28"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="30">
+        <f>'91Days pre implementation data'!A73</f>
+        <v>46107</v>
+      </c>
+      <c r="B40" s="29">
+        <f>'91Days pre implementation data'!B73</f>
+        <v>2.46</v>
+      </c>
+      <c r="C40" t="str">
+        <f>'91Days pre implementation data'!C73</f>
+        <v>Pre-Implementation Crisis Spike</v>
+      </c>
+      <c r="D40" t="str">
+        <f>'91Days pre implementation data'!D73</f>
+        <v>NC</v>
+      </c>
+      <c r="E40" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F40" s="28"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="30">
+        <f>'91Days pre implementation data'!A74</f>
+        <v>46108</v>
+      </c>
+      <c r="B41" s="29">
+        <f>'91Days pre implementation data'!B74</f>
+        <v>2.21</v>
+      </c>
+      <c r="C41" t="str">
+        <f>'91Days pre implementation data'!C74</f>
+        <v>Pre-Implementation Crisis Spike</v>
+      </c>
+      <c r="D41" t="str">
+        <f>'91Days pre implementation data'!D74</f>
+        <v>NC</v>
+      </c>
+      <c r="E41" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F41" s="28"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="30">
+        <f>'91Days pre implementation data'!A75</f>
+        <v>46109</v>
+      </c>
+      <c r="B42" s="29">
+        <f>'91Days pre implementation data'!B75</f>
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="C42" t="str">
+        <f>'91Days pre implementation data'!C75</f>
+        <v>Pre-Implementation Crisis Spike</v>
+      </c>
+      <c r="D42" t="str">
+        <f>'91Days pre implementation data'!D75</f>
+        <v>NC</v>
+      </c>
+      <c r="E42" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F42" s="28"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="30">
+        <f>'91Days pre implementation data'!A76</f>
+        <v>46110</v>
+      </c>
+      <c r="B43" s="29">
+        <f>'91Days pre implementation data'!B76</f>
+        <v>2.7</v>
+      </c>
+      <c r="C43" t="str">
+        <f>'91Days pre implementation data'!C76</f>
+        <v>Pre-Implementation Crisis Spike</v>
+      </c>
+      <c r="D43" t="str">
+        <f>'91Days pre implementation data'!D76</f>
+        <v>NC</v>
+      </c>
+      <c r="E43" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F43" s="28"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="30">
+        <f>'91Days pre implementation data'!A77</f>
+        <v>46111</v>
+      </c>
+      <c r="B44" s="29">
+        <f>'91Days pre implementation data'!B77</f>
+        <v>2.37</v>
+      </c>
+      <c r="C44" t="str">
+        <f>'91Days pre implementation data'!C77</f>
+        <v>Pre-Implementation Crisis Spike</v>
+      </c>
+      <c r="D44" t="str">
+        <f>'91Days pre implementation data'!D77</f>
+        <v>NC</v>
+      </c>
+      <c r="E44" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F44" s="28"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="30">
+        <f>'91Days pre implementation data'!A78</f>
+        <v>46112</v>
+      </c>
+      <c r="B45" s="29">
+        <f>'91Days pre implementation data'!B78</f>
+        <v>1.72</v>
+      </c>
+      <c r="C45" t="str">
+        <f>'91Days pre implementation data'!C78</f>
+        <v>Pre-Implementation Crisis Spike</v>
+      </c>
+      <c r="D45" t="str">
+        <f>'91Days pre implementation data'!D78</f>
+        <v>NC</v>
+      </c>
+      <c r="E45" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F45" s="28"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="30">
+        <f>'91Days pre implementation data'!A79</f>
+        <v>46113</v>
+      </c>
+      <c r="B46" s="29">
+        <f>'91Days pre implementation data'!B79</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C46" t="str">
+        <f>'91Days pre implementation data'!C79</f>
+        <v>Pre-Implementation Crisis Spike</v>
+      </c>
+      <c r="D46" t="str">
+        <f>'91Days pre implementation data'!D79</f>
+        <v>NC</v>
+      </c>
+      <c r="E46" t="str">
+        <f>"Pre-Implementation"</f>
+        <v>Pre-Implementation</v>
+      </c>
+      <c r="F46" s="28"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="30">
+        <f>'91Days post implementation data'!A2</f>
+        <v>46114</v>
+      </c>
+      <c r="B47" s="29">
+        <f>'91Days post implementation data'!B2</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="C47" t="str">
+        <f>'91Days post implementation data'!C2</f>
+        <v>Post-Implementation Control (Go-Live)</v>
+      </c>
+      <c r="D47" t="str">
+        <f>'91Days post implementation data'!D2</f>
+        <v>NC</v>
+      </c>
+      <c r="E47" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F47" s="28"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="30">
+        <f>'91Days post implementation data'!A3</f>
+        <v>46115</v>
+      </c>
+      <c r="B48" s="29">
+        <f>'91Days post implementation data'!B3</f>
+        <v>2.3E-2</v>
+      </c>
+      <c r="C48" t="str">
+        <f>'91Days post implementation data'!C3</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D48" t="str">
+        <f>'91Days post implementation data'!D3</f>
+        <v>C</v>
+      </c>
+      <c r="E48" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F48" s="28"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="30">
+        <f>'91Days post implementation data'!A4</f>
+        <v>46116</v>
+      </c>
+      <c r="B49" s="29">
+        <f>'91Days post implementation data'!B4</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C49" t="str">
+        <f>'91Days post implementation data'!C4</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D49" t="str">
+        <f>'91Days post implementation data'!D4</f>
+        <v>C</v>
+      </c>
+      <c r="E49" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F49" s="28"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="30">
+        <f>'91Days post implementation data'!A5</f>
+        <v>46117</v>
+      </c>
+      <c r="B50" s="29">
+        <f>'91Days post implementation data'!B5</f>
+        <v>3.1E-2</v>
+      </c>
+      <c r="C50" t="str">
+        <f>'91Days post implementation data'!C5</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D50" t="str">
+        <f>'91Days post implementation data'!D5</f>
+        <v>NC</v>
+      </c>
+      <c r="E50" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F50" s="28"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="30">
+        <f>'91Days post implementation data'!A6</f>
+        <v>46118</v>
+      </c>
+      <c r="B51" s="29">
+        <f>'91Days post implementation data'!B6</f>
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="C51" t="str">
+        <f>'91Days post implementation data'!C6</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D51" t="str">
+        <f>'91Days post implementation data'!D6</f>
+        <v>NC</v>
+      </c>
+      <c r="E51" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F51" s="28"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="30">
+        <f>'91Days post implementation data'!A7</f>
+        <v>46119</v>
+      </c>
+      <c r="B52" s="29">
+        <f>'91Days post implementation data'!B7</f>
+        <v>2.7E-2</v>
+      </c>
+      <c r="C52" t="str">
+        <f>'91Days post implementation data'!C7</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D52" t="str">
+        <f>'91Days post implementation data'!D7</f>
+        <v>C</v>
+      </c>
+      <c r="E52" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F52" s="28"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="30">
+        <f>'91Days post implementation data'!A8</f>
+        <v>46120</v>
+      </c>
+      <c r="B53" s="29">
+        <f>'91Days post implementation data'!B8</f>
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="C53" t="str">
+        <f>'91Days post implementation data'!C8</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D53" t="str">
+        <f>'91Days post implementation data'!D8</f>
+        <v>C</v>
+      </c>
+      <c r="E53" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F53" s="28"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="30">
+        <f>'91Days post implementation data'!A9</f>
+        <v>46121</v>
+      </c>
+      <c r="B54" s="29">
+        <f>'91Days post implementation data'!B9</f>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="C54" t="str">
+        <f>'91Days post implementation data'!C9</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D54" t="str">
+        <f>'91Days post implementation data'!D9</f>
+        <v>NC</v>
+      </c>
+      <c r="E54" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F54" s="28"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="30">
+        <f>'91Days post implementation data'!A10</f>
+        <v>46122</v>
+      </c>
+      <c r="B55" s="29">
+        <f>'91Days post implementation data'!B10</f>
+        <v>3.1E-2</v>
+      </c>
+      <c r="C55" t="str">
+        <f>'91Days post implementation data'!C10</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D55" t="str">
+        <f>'91Days post implementation data'!D10</f>
+        <v>NC</v>
+      </c>
+      <c r="E55" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F55" s="28"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="30">
+        <f>'91Days post implementation data'!A11</f>
+        <v>46123</v>
+      </c>
+      <c r="B56" s="29">
+        <f>'91Days post implementation data'!B11</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="C56" t="str">
+        <f>'91Days post implementation data'!C11</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D56" t="str">
+        <f>'91Days post implementation data'!D11</f>
+        <v>NC</v>
+      </c>
+      <c r="E56" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F56" s="28"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="30">
+        <f>'91Days post implementation data'!A12</f>
+        <v>46124</v>
+      </c>
+      <c r="B57" s="29">
+        <f>'91Days post implementation data'!B12</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C57" t="str">
+        <f>'91Days post implementation data'!C12</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D57" t="str">
+        <f>'91Days post implementation data'!D12</f>
+        <v>C</v>
+      </c>
+      <c r="E57" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F57" s="28"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="30">
+        <f>'91Days post implementation data'!A13</f>
+        <v>46125</v>
+      </c>
+      <c r="B58" s="29">
+        <f>'91Days post implementation data'!B13</f>
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="C58" t="str">
+        <f>'91Days post implementation data'!C13</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D58" t="str">
+        <f>'91Days post implementation data'!D13</f>
+        <v>NC</v>
+      </c>
+      <c r="E58" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F58" s="28"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="30">
+        <f>'91Days post implementation data'!A14</f>
+        <v>46126</v>
+      </c>
+      <c r="B59" s="29">
+        <f>'91Days post implementation data'!B14</f>
+        <v>0.03</v>
+      </c>
+      <c r="C59" t="str">
+        <f>'91Days post implementation data'!C14</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D59" t="str">
+        <f>'91Days post implementation data'!D14</f>
+        <v>NC</v>
+      </c>
+      <c r="E59" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F59" s="28"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="30">
+        <f>'91Days post implementation data'!A15</f>
+        <v>46127</v>
+      </c>
+      <c r="B60" s="29">
+        <f>'91Days post implementation data'!B15</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C60" t="str">
+        <f>'91Days post implementation data'!C15</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D60" t="str">
+        <f>'91Days post implementation data'!D15</f>
+        <v>C</v>
+      </c>
+      <c r="E60" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F60" s="28"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="30">
+        <f>'91Days post implementation data'!A16</f>
+        <v>46128</v>
+      </c>
+      <c r="B61" s="29">
+        <f>'91Days post implementation data'!B16</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C61" t="str">
+        <f>'91Days post implementation data'!C16</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D61" t="str">
+        <f>'91Days post implementation data'!D16</f>
+        <v>C</v>
+      </c>
+      <c r="E61" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F61" s="28"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="30">
+        <f>'91Days post implementation data'!A17</f>
+        <v>46129</v>
+      </c>
+      <c r="B62" s="29">
+        <f>'91Days post implementation data'!B17</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C62" t="str">
+        <f>'91Days post implementation data'!C17</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D62" t="str">
+        <f>'91Days post implementation data'!D17</f>
+        <v>C</v>
+      </c>
+      <c r="E62" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F62" s="28"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="30">
+        <f>'91Days post implementation data'!A18</f>
+        <v>46130</v>
+      </c>
+      <c r="B63" s="29">
+        <f>'91Days post implementation data'!B18</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C63" t="str">
+        <f>'91Days post implementation data'!C18</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D63" t="str">
+        <f>'91Days post implementation data'!D18</f>
+        <v>C</v>
+      </c>
+      <c r="E63" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F63" s="28"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="30">
+        <f>'91Days post implementation data'!A19</f>
+        <v>46131</v>
+      </c>
+      <c r="B64" s="29">
+        <f>'91Days post implementation data'!B19</f>
+        <v>2.86E-2</v>
+      </c>
+      <c r="C64" t="str">
+        <f>'91Days post implementation data'!C19</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D64" t="str">
+        <f>'91Days post implementation data'!D19</f>
+        <v>C</v>
+      </c>
+      <c r="E64" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F64" s="28"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="30">
+        <f>'91Days post implementation data'!A20</f>
+        <v>46132</v>
+      </c>
+      <c r="B65" s="29">
+        <f>'91Days post implementation data'!B20</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C65" t="str">
+        <f>'91Days post implementation data'!C20</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D65" t="str">
+        <f>'91Days post implementation data'!D20</f>
+        <v>C</v>
+      </c>
+      <c r="E65" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F65" s="28"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="30">
+        <f>'91Days post implementation data'!A21</f>
+        <v>46133</v>
+      </c>
+      <c r="B66" s="29">
+        <f>'91Days post implementation data'!B21</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C66" t="str">
+        <f>'91Days post implementation data'!C21</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D66" t="str">
+        <f>'91Days post implementation data'!D21</f>
+        <v>C</v>
+      </c>
+      <c r="E66" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F66" s="28"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="30">
+        <f>'91Days post implementation data'!A22</f>
+        <v>46134</v>
+      </c>
+      <c r="B67" s="29">
+        <f>'91Days post implementation data'!B22</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C67" t="str">
+        <f>'91Days post implementation data'!C22</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D67" t="str">
+        <f>'91Days post implementation data'!D22</f>
+        <v>C</v>
+      </c>
+      <c r="E67" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F67" s="28"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="30">
+        <f>'91Days post implementation data'!A23</f>
+        <v>46135</v>
+      </c>
+      <c r="B68" s="29">
+        <f>'91Days post implementation data'!B23</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C68" t="str">
+        <f>'91Days post implementation data'!C23</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D68" t="str">
+        <f>'91Days post implementation data'!D23</f>
+        <v>C</v>
+      </c>
+      <c r="E68" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F68" s="28"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="30">
+        <f>'91Days post implementation data'!A24</f>
+        <v>46136</v>
+      </c>
+      <c r="B69" s="29">
+        <f>'91Days post implementation data'!B24</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C69" t="str">
+        <f>'91Days post implementation data'!C24</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D69" t="str">
+        <f>'91Days post implementation data'!D24</f>
+        <v>C</v>
+      </c>
+      <c r="E69" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F69" s="28"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="30">
+        <f>'91Days post implementation data'!A25</f>
+        <v>46137</v>
+      </c>
+      <c r="B70" s="29">
+        <f>'91Days post implementation data'!B25</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C70" t="str">
+        <f>'91Days post implementation data'!C25</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D70" t="str">
+        <f>'91Days post implementation data'!D25</f>
+        <v>C</v>
+      </c>
+      <c r="E70" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F70" s="28"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="30">
+        <f>'91Days post implementation data'!A26</f>
+        <v>46138</v>
+      </c>
+      <c r="B71" s="29">
+        <f>'91Days post implementation data'!B26</f>
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="C71" t="str">
+        <f>'91Days post implementation data'!C26</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D71" t="str">
+        <f>'91Days post implementation data'!D26</f>
+        <v>C</v>
+      </c>
+      <c r="E71" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F71" s="28"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="30">
+        <f>'91Days post implementation data'!A27</f>
+        <v>46139</v>
+      </c>
+      <c r="B72" s="29">
+        <f>'91Days post implementation data'!B27</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C72" t="str">
+        <f>'91Days post implementation data'!C27</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D72" t="str">
+        <f>'91Days post implementation data'!D27</f>
+        <v>C</v>
+      </c>
+      <c r="E72" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F72" s="28"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="30">
+        <f>'91Days post implementation data'!A28</f>
+        <v>46140</v>
+      </c>
+      <c r="B73" s="29">
+        <f>'91Days post implementation data'!B28</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C73" t="str">
+        <f>'91Days post implementation data'!C28</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D73" t="str">
+        <f>'91Days post implementation data'!D28</f>
+        <v>C</v>
+      </c>
+      <c r="E73" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F73" s="28"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="30">
+        <f>'91Days post implementation data'!A29</f>
+        <v>46141</v>
+      </c>
+      <c r="B74" s="29">
+        <f>'91Days post implementation data'!B29</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C74" t="str">
+        <f>'91Days post implementation data'!C29</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D74" t="str">
+        <f>'91Days post implementation data'!D29</f>
+        <v>C</v>
+      </c>
+      <c r="E74" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F74" s="28"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="30">
+        <f>'91Days post implementation data'!A30</f>
+        <v>46142</v>
+      </c>
+      <c r="B75" s="29">
+        <f>'91Days post implementation data'!B30</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C75" t="str">
+        <f>'91Days post implementation data'!C30</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D75" t="str">
+        <f>'91Days post implementation data'!D30</f>
+        <v>C</v>
+      </c>
+      <c r="E75" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F75" s="28"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="30">
+        <f>'91Days post implementation data'!A31</f>
+        <v>46143</v>
+      </c>
+      <c r="B76" s="29">
+        <f>'91Days post implementation data'!B31</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C76" t="str">
+        <f>'91Days post implementation data'!C31</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D76" t="str">
+        <f>'91Days post implementation data'!D31</f>
+        <v>C</v>
+      </c>
+      <c r="E76" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F76" s="28"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="30">
+        <f>'91Days post implementation data'!A32</f>
+        <v>46144</v>
+      </c>
+      <c r="B77" s="29">
+        <f>'91Days post implementation data'!B32</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C77" t="str">
+        <f>'91Days post implementation data'!C32</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D77" t="str">
+        <f>'91Days post implementation data'!D32</f>
+        <v>C</v>
+      </c>
+      <c r="E77" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F77" s="28"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="30">
+        <f>'91Days post implementation data'!A33</f>
+        <v>46145</v>
+      </c>
+      <c r="B78" s="29">
+        <f>'91Days post implementation data'!B33</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C78" t="str">
+        <f>'91Days post implementation data'!C33</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D78" t="str">
+        <f>'91Days post implementation data'!D33</f>
+        <v>C</v>
+      </c>
+      <c r="E78" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F78" s="28"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="30">
+        <f>'91Days post implementation data'!A34</f>
+        <v>46146</v>
+      </c>
+      <c r="B79" s="29">
+        <f>'91Days post implementation data'!B34</f>
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="C79" t="str">
+        <f>'91Days post implementation data'!C34</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D79" t="str">
+        <f>'91Days post implementation data'!D34</f>
+        <v>C</v>
+      </c>
+      <c r="E79" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F79" s="28"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="30">
+        <f>'91Days post implementation data'!A35</f>
+        <v>46147</v>
+      </c>
+      <c r="B80" s="29">
+        <f>'91Days post implementation data'!B35</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C80" t="str">
+        <f>'91Days post implementation data'!C35</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D80" t="str">
+        <f>'91Days post implementation data'!D35</f>
+        <v>C</v>
+      </c>
+      <c r="E80" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F80" s="28"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="30">
+        <f>'91Days post implementation data'!A36</f>
+        <v>46148</v>
+      </c>
+      <c r="B81" s="29">
+        <f>'91Days post implementation data'!B36</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C81" t="str">
+        <f>'91Days post implementation data'!C36</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D81" t="str">
+        <f>'91Days post implementation data'!D36</f>
+        <v>C</v>
+      </c>
+      <c r="E81" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F81" s="28"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="30">
+        <f>'91Days post implementation data'!A37</f>
+        <v>46149</v>
+      </c>
+      <c r="B82" s="29">
+        <f>'91Days post implementation data'!B37</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C82" t="str">
+        <f>'91Days post implementation data'!C37</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D82" t="str">
+        <f>'91Days post implementation data'!D37</f>
+        <v>C</v>
+      </c>
+      <c r="E82" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F82" s="28"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="30">
+        <f>'91Days post implementation data'!A38</f>
+        <v>46150</v>
+      </c>
+      <c r="B83" s="29">
+        <f>'91Days post implementation data'!B38</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C83" t="str">
+        <f>'91Days post implementation data'!C38</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D83" t="str">
+        <f>'91Days post implementation data'!D38</f>
+        <v>C</v>
+      </c>
+      <c r="E83" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F83" s="28"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="30">
+        <f>'91Days post implementation data'!A39</f>
+        <v>46151</v>
+      </c>
+      <c r="B84" s="29">
+        <f>'91Days post implementation data'!B39</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C84" t="str">
+        <f>'91Days post implementation data'!C39</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D84" t="str">
+        <f>'91Days post implementation data'!D39</f>
+        <v>C</v>
+      </c>
+      <c r="E84" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F84" s="28"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="30">
+        <f>'91Days post implementation data'!A40</f>
+        <v>46152</v>
+      </c>
+      <c r="B85" s="29">
+        <f>'91Days post implementation data'!B40</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C85" t="str">
+        <f>'91Days post implementation data'!C40</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D85" t="str">
+        <f>'91Days post implementation data'!D40</f>
+        <v>C</v>
+      </c>
+      <c r="E85" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F85" s="28"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="30">
+        <f>'91Days post implementation data'!A41</f>
+        <v>46153</v>
+      </c>
+      <c r="B86" s="29">
+        <f>'91Days post implementation data'!B41</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C86" t="str">
+        <f>'91Days post implementation data'!C41</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D86" t="str">
+        <f>'91Days post implementation data'!D41</f>
+        <v>C</v>
+      </c>
+      <c r="E86" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F86" s="28"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="30">
+        <f>'91Days post implementation data'!A42</f>
+        <v>46154</v>
+      </c>
+      <c r="B87" s="29">
+        <f>'91Days post implementation data'!B42</f>
+        <v>2.87E-2</v>
+      </c>
+      <c r="C87" t="str">
+        <f>'91Days post implementation data'!C42</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D87" t="str">
+        <f>'91Days post implementation data'!D42</f>
+        <v>C</v>
+      </c>
+      <c r="E87" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F87" s="28"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="30">
+        <f>'91Days post implementation data'!A43</f>
+        <v>46155</v>
+      </c>
+      <c r="B88" s="29">
+        <f>'91Days post implementation data'!B43</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C88" t="str">
+        <f>'91Days post implementation data'!C43</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D88" t="str">
+        <f>'91Days post implementation data'!D43</f>
+        <v>C</v>
+      </c>
+      <c r="E88" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F88" s="28"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="30">
+        <f>'91Days post implementation data'!A44</f>
+        <v>46156</v>
+      </c>
+      <c r="B89" s="29">
+        <f>'91Days post implementation data'!B44</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C89" t="str">
+        <f>'91Days post implementation data'!C44</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D89" t="str">
+        <f>'91Days post implementation data'!D44</f>
+        <v>C</v>
+      </c>
+      <c r="E89" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F89" s="28"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="30">
+        <f>'91Days post implementation data'!A45</f>
+        <v>46157</v>
+      </c>
+      <c r="B90" s="29">
+        <f>'91Days post implementation data'!B45</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C90" t="str">
+        <f>'91Days post implementation data'!C45</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D90" t="str">
+        <f>'91Days post implementation data'!D45</f>
+        <v>C</v>
+      </c>
+      <c r="E90" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F90" s="28"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="30">
+        <f>'91Days post implementation data'!A46</f>
+        <v>46158</v>
+      </c>
+      <c r="B91" s="29">
+        <f>'91Days post implementation data'!B46</f>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C91" t="str">
+        <f>'91Days post implementation data'!C46</f>
+        <v>Post-Implementation Control</v>
+      </c>
+      <c r="D91" t="str">
+        <f>'91Days post implementation data'!D46</f>
+        <v>C</v>
+      </c>
+      <c r="E91" t="str">
+        <f>"Post-Implementation"</f>
+        <v>Post-Implementation</v>
+      </c>
+      <c r="F91" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="G15:L19"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="G25:L32"/>
+    <mergeCell ref="G6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B1DB30-19A1-41AB-9DA5-67F48316EF0E}">
+  <dimension ref="A1:M92"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="4"/>
+    <col min="9" max="10" width="30.5703125" style="4" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46114</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="7">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="4" t="str">
         <f>IF(B2&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="21">
+      <c r="G2" s="3">
         <f>PERCENTILE(B2:B92,0.5)</f>
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46115</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
         <v>2.3E-2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="str">
+      <c r="C3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="4" t="str">
         <f>IF(B3&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="21">
+      <c r="G3" s="3">
         <f>PERCENTILE(B2:B92,0.25)</f>
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46116</v>
       </c>
-      <c r="B4" s="2">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2" t="str">
+      <c r="B4" s="7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="4" t="str">
         <f>IF(B4&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46117</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <v>3.1E-2</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2" t="str">
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="str">
         <f>IF(B5&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46118</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="7">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2" t="str">
+      <c r="C6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="4" t="str">
         <f>IF(B6&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="F6" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="12"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G6" s="27"/>
+      <c r="I6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46119</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="7">
         <v>2.7E-2</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="str">
+      <c r="C7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="4" t="str">
         <f>IF(B7&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="7">
         <f>COUNTIF(D2:D92,"NC")</f>
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46120</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="7">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2" t="str">
+      <c r="C8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="4" t="str">
         <f>IF(B8&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="7">
         <f>COUNT(A2:A92)</f>
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46121</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="7">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="str">
+      <c r="C9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4" t="str">
         <f>IF(B9&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="2">
-        <f>F7/F8</f>
+      <c r="G9" s="8">
+        <f>G7/G8</f>
         <v>8.7912087912087919E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46122</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="7">
         <v>3.1E-2</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="2" t="str">
+      <c r="C10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="4" t="str">
         <f>IF(B10&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="2">
-        <f>F9*1000000</f>
+      <c r="G10" s="10">
+        <f>G9*1000000</f>
         <v>87912.087912087925</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46123</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="7">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2" t="str">
+      <c r="C11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="4" t="str">
         <f>IF(B11&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="2">
-        <f>NORMSINV(1-F9)</f>
+      <c r="G11" s="8">
+        <f>NORMSINV(1-G9)</f>
         <v>1.3537248536782602</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46124</v>
       </c>
-      <c r="B12" s="2">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="2" t="str">
+      <c r="B12" s="7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="4" t="str">
         <f>IF(B12&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46125</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="7">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="2" t="str">
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4" t="str">
         <f>IF(B13&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46126</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="7">
         <v>0.03</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="2" t="str">
+      <c r="C14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="4" t="str">
         <f>IF(B14&gt;$G$3,"NC","C")</f>
         <v>NC</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="F14" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="18"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46127</v>
       </c>
-      <c r="B15" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="2" t="str">
+      <c r="B15" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="4" t="str">
         <f>IF(B15&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E15" s="4" t="str">
-        <f>"To sustain a stable Daily Reporting Latency where P50 and P25 are both "&amp;TEXT(G2,"0.000")&amp;" hours, maintain fewer than 10 NC days per 91-day cycle, and progressively reduce residual variation toward zero defects."</f>
-        <v>To sustain a stable Daily Reporting Latency where P50 and P25 are both 0.029 hours, maintain fewer than 10 NC days per 91-day cycle, and progressively reduce residual variation toward zero defects.</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F15" s="11" t="str">
+        <f>"To sustain Daily Reporting Latency at P50 = "&amp;TEXT(G2,"0.000")&amp;" hours and P25 = "&amp;TEXT(G3,"0.000")&amp;" hours, while reducing non-compliant runs from "&amp;G7&amp;" to no more than 2 per 91-day control cycle. This will lower DPMO from "&amp;TEXT(G10,"#,##0")&amp;" to no more than 22,000 and raise process capability from "&amp;TEXT(G11,"0.0000")&amp;" sigma to at least 2.00 sigma as the next demonstrated performance threshold."</f>
+        <v>To sustain Daily Reporting Latency at P50 = 0.029 hours and P25 = 0.029 hours, while reducing non-compliant runs from 8 to no more than 2 per 91-day control cycle. This will lower DPMO from 87,912 to no more than 22,000 and raise process capability from 1.3537 sigma to at least 2.00 sigma as the next demonstrated performance threshold.</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="13"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46128</v>
       </c>
-      <c r="B16" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="2" t="str">
+      <c r="B16" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="4" t="str">
         <f>IF(B16&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="16"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46129</v>
       </c>
-      <c r="B17" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="2" t="str">
+      <c r="B17" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="4" t="str">
         <f>IF(B17&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F17" s="14"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="16"/>
+    </row>
+    <row r="18" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46130</v>
       </c>
-      <c r="B18" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="2" t="str">
+      <c r="B18" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="4" t="str">
         <f>IF(B18&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F18" s="17"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="19"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46131</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="8">
         <v>2.86E-2</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="2" t="str">
+      <c r="C19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="4" t="str">
         <f>IF(B19&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46132</v>
       </c>
-      <c r="B20" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="2" t="str">
+      <c r="B20" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="4" t="str">
         <f>IF(B20&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46133</v>
       </c>
-      <c r="B21" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="2" t="str">
+      <c r="B21" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="4" t="str">
         <f>IF(B21&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46134</v>
       </c>
-      <c r="B22" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="2" t="str">
+      <c r="B22" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="4" t="str">
         <f>IF(B22&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E22" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="18"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F22" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="26"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46135</v>
       </c>
-      <c r="B23" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="2" t="str">
+      <c r="B23" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="4" t="str">
         <f>IF(B23&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E23" s="3" t="str">
-        <f>"The post-implementation process is centered and stabilized, with P50 and P25 both at "&amp;TEXT(G2,"0.000")&amp;" hours. However, residual upper-tail variation caused "&amp;F7&amp;" of "&amp;F8&amp;" days to exceed the statistical threshold, resulting in an NC rate of "&amp;TEXT(F9,"0.00%")&amp;", "&amp;TEXT(F10,"#,##0.0")&amp;" DPMO, and a process sigma score of "&amp;TEXT(F11,"0.0000")&amp;" sigma."</f>
-        <v>The post-implementation process is centered and stabilized, with P50 and P25 both at 0.029 hours. However, residual upper-tail variation caused 8 of 91 days to exceed the statistical threshold, resulting in an NC rate of 8.79%, 87,912.1 DPMO, and a process sigma score of 1.3537 sigma.</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="5"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F23" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="13"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46136</v>
       </c>
-      <c r="B24" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="2" t="str">
+      <c r="B24" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="4" t="str">
         <f>IF(B24&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="8"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="16"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46137</v>
       </c>
-      <c r="B25" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="2" t="str">
+      <c r="B25" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="4" t="str">
         <f>IF(B25&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="8"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F25" s="14"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="16"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46138</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="8">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="2" t="str">
+      <c r="C26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="4" t="str">
         <f>IF(B26&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="8"/>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F26" s="14"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="16"/>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46139</v>
       </c>
-      <c r="B27" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="2" t="str">
+      <c r="B27" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="4" t="str">
         <f>IF(B27&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="11"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="19"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46140</v>
       </c>
-      <c r="B28" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="2" t="str">
+      <c r="B28" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="4" t="str">
         <f>IF(B28&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46141</v>
       </c>
-      <c r="B29" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="2" t="str">
+      <c r="B29" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="4" t="str">
         <f>IF(B29&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46142</v>
       </c>
-      <c r="B30" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="2" t="str">
+      <c r="B30" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="4" t="str">
         <f>IF(B30&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46143</v>
       </c>
-      <c r="B31" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="2" t="str">
+      <c r="B31" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="4" t="str">
         <f>IF(B31&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46144</v>
       </c>
-      <c r="B32" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="2" t="str">
+      <c r="B32" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="4" t="str">
         <f>IF(B32&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2843,13 +5595,13 @@
       <c r="A33" s="1">
         <v>46145</v>
       </c>
-      <c r="B33" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="2" t="str">
+      <c r="B33" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="4" t="str">
         <f>IF(B33&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2858,13 +5610,13 @@
       <c r="A34" s="1">
         <v>46146</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="8">
         <v>2.8400000000000002E-2</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="2" t="str">
+      <c r="C34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="4" t="str">
         <f>IF(B34&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2873,13 +5625,13 @@
       <c r="A35" s="1">
         <v>46147</v>
       </c>
-      <c r="B35" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="2" t="str">
+      <c r="B35" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="4" t="str">
         <f>IF(B35&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2888,13 +5640,13 @@
       <c r="A36" s="1">
         <v>46148</v>
       </c>
-      <c r="B36" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="2" t="str">
+      <c r="B36" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="4" t="str">
         <f>IF(B36&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2903,13 +5655,13 @@
       <c r="A37" s="1">
         <v>46149</v>
       </c>
-      <c r="B37" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="2" t="str">
+      <c r="B37" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="4" t="str">
         <f>IF(B37&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2918,13 +5670,13 @@
       <c r="A38" s="1">
         <v>46150</v>
       </c>
-      <c r="B38" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="2" t="str">
+      <c r="B38" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="4" t="str">
         <f>IF(B38&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2933,13 +5685,13 @@
       <c r="A39" s="1">
         <v>46151</v>
       </c>
-      <c r="B39" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="2" t="str">
+      <c r="B39" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="4" t="str">
         <f>IF(B39&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2948,13 +5700,13 @@
       <c r="A40" s="1">
         <v>46152</v>
       </c>
-      <c r="B40" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="2" t="str">
+      <c r="B40" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="4" t="str">
         <f>IF(B40&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2963,13 +5715,13 @@
       <c r="A41" s="1">
         <v>46153</v>
       </c>
-      <c r="B41" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="2" t="str">
+      <c r="B41" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="4" t="str">
         <f>IF(B41&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2978,13 +5730,13 @@
       <c r="A42" s="1">
         <v>46154</v>
       </c>
-      <c r="B42" s="19">
+      <c r="B42" s="8">
         <v>2.87E-2</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="2" t="str">
+      <c r="C42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="4" t="str">
         <f>IF(B42&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -2993,13 +5745,13 @@
       <c r="A43" s="1">
         <v>46155</v>
       </c>
-      <c r="B43" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="2" t="str">
+      <c r="B43" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="4" t="str">
         <f>IF(B43&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3008,13 +5760,13 @@
       <c r="A44" s="1">
         <v>46156</v>
       </c>
-      <c r="B44" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="2" t="str">
+      <c r="B44" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="4" t="str">
         <f>IF(B44&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3023,13 +5775,13 @@
       <c r="A45" s="1">
         <v>46157</v>
       </c>
-      <c r="B45" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="2" t="str">
+      <c r="B45" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="4" t="str">
         <f>IF(B45&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3038,13 +5790,13 @@
       <c r="A46" s="1">
         <v>46158</v>
       </c>
-      <c r="B46" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="2" t="str">
+      <c r="B46" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="4" t="str">
         <f>IF(B46&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3053,13 +5805,13 @@
       <c r="A47" s="1">
         <v>46159</v>
       </c>
-      <c r="B47" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="2" t="str">
+      <c r="B47" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="4" t="str">
         <f>IF(B47&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3068,13 +5820,13 @@
       <c r="A48" s="1">
         <v>46160</v>
       </c>
-      <c r="B48" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" s="2" t="str">
+      <c r="B48" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="4" t="str">
         <f>IF(B48&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3083,13 +5835,13 @@
       <c r="A49" s="1">
         <v>46161</v>
       </c>
-      <c r="B49" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="2" t="str">
+      <c r="B49" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="4" t="str">
         <f>IF(B49&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3098,13 +5850,13 @@
       <c r="A50" s="1">
         <v>46162</v>
       </c>
-      <c r="B50" s="19">
+      <c r="B50" s="8">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="2" t="str">
+      <c r="C50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="4" t="str">
         <f>IF(B50&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3113,13 +5865,13 @@
       <c r="A51" s="1">
         <v>46163</v>
       </c>
-      <c r="B51" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="2" t="str">
+      <c r="B51" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="4" t="str">
         <f>IF(B51&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3128,13 +5880,13 @@
       <c r="A52" s="1">
         <v>46164</v>
       </c>
-      <c r="B52" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" s="2" t="str">
+      <c r="B52" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="4" t="str">
         <f>IF(B52&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3143,13 +5895,13 @@
       <c r="A53" s="1">
         <v>46165</v>
       </c>
-      <c r="B53" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="2" t="str">
+      <c r="B53" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="4" t="str">
         <f>IF(B53&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3158,13 +5910,13 @@
       <c r="A54" s="1">
         <v>46166</v>
       </c>
-      <c r="B54" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="2" t="str">
+      <c r="B54" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="4" t="str">
         <f>IF(B54&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3173,13 +5925,13 @@
       <c r="A55" s="1">
         <v>46167</v>
       </c>
-      <c r="B55" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="2" t="str">
+      <c r="B55" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="4" t="str">
         <f>IF(B55&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3188,13 +5940,13 @@
       <c r="A56" s="1">
         <v>46168</v>
       </c>
-      <c r="B56" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="2" t="str">
+      <c r="B56" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="4" t="str">
         <f>IF(B56&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3203,13 +5955,13 @@
       <c r="A57" s="1">
         <v>46169</v>
       </c>
-      <c r="B57" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="2" t="str">
+      <c r="B57" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="4" t="str">
         <f>IF(B57&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3218,13 +5970,13 @@
       <c r="A58" s="1">
         <v>46170</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="8">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D58" s="2" t="str">
+      <c r="C58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="4" t="str">
         <f>IF(B58&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3233,13 +5985,13 @@
       <c r="A59" s="1">
         <v>46171</v>
       </c>
-      <c r="B59" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D59" s="2" t="str">
+      <c r="B59" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="4" t="str">
         <f>IF(B59&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3248,13 +6000,13 @@
       <c r="A60" s="1">
         <v>46172</v>
       </c>
-      <c r="B60" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="2" t="str">
+      <c r="B60" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="4" t="str">
         <f>IF(B60&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3263,13 +6015,13 @@
       <c r="A61" s="1">
         <v>46173</v>
       </c>
-      <c r="B61" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D61" s="2" t="str">
+      <c r="B61" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="4" t="str">
         <f>IF(B61&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3278,13 +6030,13 @@
       <c r="A62" s="1">
         <v>46174</v>
       </c>
-      <c r="B62" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62" s="2" t="str">
+      <c r="B62" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="4" t="str">
         <f>IF(B62&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3293,13 +6045,13 @@
       <c r="A63" s="1">
         <v>46175</v>
       </c>
-      <c r="B63" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D63" s="2" t="str">
+      <c r="B63" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="4" t="str">
         <f>IF(B63&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3308,13 +6060,13 @@
       <c r="A64" s="1">
         <v>46176</v>
       </c>
-      <c r="B64" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D64" s="2" t="str">
+      <c r="B64" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" s="4" t="str">
         <f>IF(B64&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3323,13 +6075,13 @@
       <c r="A65" s="1">
         <v>46177</v>
       </c>
-      <c r="B65" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D65" s="2" t="str">
+      <c r="B65" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="4" t="str">
         <f>IF(B65&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3338,13 +6090,13 @@
       <c r="A66" s="1">
         <v>46178</v>
       </c>
-      <c r="B66" s="19">
+      <c r="B66" s="8">
         <v>2.86E-2</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D66" s="2" t="str">
+      <c r="C66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="4" t="str">
         <f>IF(B66&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3353,13 +6105,13 @@
       <c r="A67" s="1">
         <v>46179</v>
       </c>
-      <c r="B67" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D67" s="2" t="str">
+      <c r="B67" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="4" t="str">
         <f>IF(B67&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3368,13 +6120,13 @@
       <c r="A68" s="1">
         <v>46180</v>
       </c>
-      <c r="B68" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D68" s="2" t="str">
+      <c r="B68" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="4" t="str">
         <f>IF(B68&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3383,13 +6135,13 @@
       <c r="A69" s="1">
         <v>46181</v>
       </c>
-      <c r="B69" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D69" s="2" t="str">
+      <c r="B69" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" s="4" t="str">
         <f>IF(B69&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3398,13 +6150,13 @@
       <c r="A70" s="1">
         <v>46182</v>
       </c>
-      <c r="B70" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D70" s="2" t="str">
+      <c r="B70" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" s="4" t="str">
         <f>IF(B70&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3413,13 +6165,13 @@
       <c r="A71" s="1">
         <v>46183</v>
       </c>
-      <c r="B71" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" s="2" t="str">
+      <c r="B71" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" s="4" t="str">
         <f>IF(B71&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3428,13 +6180,13 @@
       <c r="A72" s="1">
         <v>46184</v>
       </c>
-      <c r="B72" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D72" s="2" t="str">
+      <c r="B72" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="4" t="str">
         <f>IF(B72&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3443,13 +6195,13 @@
       <c r="A73" s="1">
         <v>46185</v>
       </c>
-      <c r="B73" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D73" s="2" t="str">
+      <c r="B73" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" s="4" t="str">
         <f>IF(B73&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3458,13 +6210,13 @@
       <c r="A74" s="1">
         <v>46186</v>
       </c>
-      <c r="B74" s="19">
+      <c r="B74" s="8">
         <v>2.87E-2</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D74" s="2" t="str">
+      <c r="C74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="4" t="str">
         <f>IF(B74&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3473,13 +6225,13 @@
       <c r="A75" s="1">
         <v>46187</v>
       </c>
-      <c r="B75" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D75" s="2" t="str">
+      <c r="B75" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="4" t="str">
         <f>IF(B75&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3488,13 +6240,13 @@
       <c r="A76" s="1">
         <v>46188</v>
       </c>
-      <c r="B76" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D76" s="2" t="str">
+      <c r="B76" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" s="4" t="str">
         <f>IF(B76&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3503,13 +6255,13 @@
       <c r="A77" s="1">
         <v>46189</v>
       </c>
-      <c r="B77" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D77" s="2" t="str">
+      <c r="B77" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="4" t="str">
         <f>IF(B77&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3518,13 +6270,13 @@
       <c r="A78" s="1">
         <v>46190</v>
       </c>
-      <c r="B78" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D78" s="2" t="str">
+      <c r="B78" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="4" t="str">
         <f>IF(B78&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3533,13 +6285,13 @@
       <c r="A79" s="1">
         <v>46191</v>
       </c>
-      <c r="B79" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D79" s="2" t="str">
+      <c r="B79" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" s="4" t="str">
         <f>IF(B79&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3548,13 +6300,13 @@
       <c r="A80" s="1">
         <v>46192</v>
       </c>
-      <c r="B80" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D80" s="2" t="str">
+      <c r="B80" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="4" t="str">
         <f>IF(B80&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3563,13 +6315,13 @@
       <c r="A81" s="1">
         <v>46193</v>
       </c>
-      <c r="B81" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D81" s="2" t="str">
+      <c r="B81" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" s="4" t="str">
         <f>IF(B81&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3578,13 +6330,13 @@
       <c r="A82" s="1">
         <v>46194</v>
       </c>
-      <c r="B82" s="19">
+      <c r="B82" s="8">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D82" s="2" t="str">
+      <c r="C82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" s="4" t="str">
         <f>IF(B82&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3593,13 +6345,13 @@
       <c r="A83" s="1">
         <v>46195</v>
       </c>
-      <c r="B83" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D83" s="2" t="str">
+      <c r="B83" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="4" t="str">
         <f>IF(B83&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3608,13 +6360,13 @@
       <c r="A84" s="1">
         <v>46196</v>
       </c>
-      <c r="B84" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D84" s="2" t="str">
+      <c r="B84" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="4" t="str">
         <f>IF(B84&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3623,13 +6375,13 @@
       <c r="A85" s="1">
         <v>46197</v>
       </c>
-      <c r="B85" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D85" s="2" t="str">
+      <c r="B85" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="4" t="str">
         <f>IF(B85&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3638,13 +6390,13 @@
       <c r="A86" s="1">
         <v>46198</v>
       </c>
-      <c r="B86" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D86" s="2" t="str">
+      <c r="B86" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" s="4" t="str">
         <f>IF(B86&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3653,13 +6405,13 @@
       <c r="A87" s="1">
         <v>46199</v>
       </c>
-      <c r="B87" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D87" s="2" t="str">
+      <c r="B87" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="4" t="str">
         <f>IF(B87&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3668,13 +6420,13 @@
       <c r="A88" s="1">
         <v>46200</v>
       </c>
-      <c r="B88" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D88" s="2" t="str">
+      <c r="B88" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D88" s="4" t="str">
         <f>IF(B88&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3683,13 +6435,13 @@
       <c r="A89" s="1">
         <v>46201</v>
       </c>
-      <c r="B89" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D89" s="2" t="str">
+      <c r="B89" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" s="4" t="str">
         <f>IF(B89&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3698,13 +6450,13 @@
       <c r="A90" s="1">
         <v>46202</v>
       </c>
-      <c r="B90" s="19">
+      <c r="B90" s="8">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D90" s="2" t="str">
+      <c r="C90" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="4" t="str">
         <f>IF(B90&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3713,13 +6465,13 @@
       <c r="A91" s="1">
         <v>46203</v>
       </c>
-      <c r="B91" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D91" s="2" t="str">
+      <c r="B91" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" s="4" t="str">
         <f>IF(B91&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
@@ -3728,26 +6480,29 @@
       <c r="A92" s="1">
         <v>46204</v>
       </c>
-      <c r="B92" s="19">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="B92" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D92" s="2" t="str">
+      <c r="D92" s="4" t="str">
         <f>IF(B92&gt;$G$3,"NC","C")</f>
         <v>C</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E14:K14"/>
-    <mergeCell ref="E22:K22"/>
-    <mergeCell ref="E23:K27"/>
-    <mergeCell ref="E15:K18"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F14:L14"/>
+    <mergeCell ref="F22:L22"/>
+    <mergeCell ref="F23:L27"/>
+    <mergeCell ref="F15:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>